--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98627</v>
+        <v>98629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128947201</v>
       </c>
       <c r="B2" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128947201</v>
+        <v>70537719</v>
       </c>
       <c r="B2" t="n">
-        <v>98641</v>
+        <v>8444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spicksten, Srm</t>
+          <t>Kyrkkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573505</v>
+        <v>573710</v>
       </c>
       <c r="R2" t="n">
-        <v>6521741</v>
+        <v>6521751</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2018-04-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2018-04-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,23 +766,222 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128947201</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Spicksten, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>573505</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6521741</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jenny Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Jenny Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128947190</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Spicksten, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>573317</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6521806</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45530-2023 artfynd.xlsx
+++ b/artfynd/A 45530-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70537719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947201</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,8 +997,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947190</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>